--- a/rcads/data/xls/81_Agents.xlsx
+++ b/rcads/data/xls/81_Agents.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_81_Agents"/>
   </sheets>
   <definedNames>
-    <definedName name="_81_Agents">'_81_Agents'!$A$1:$C$52</definedName>
+    <definedName name="_81_Agents">'_81_Agents'!$A$1:$C$55</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -948,6 +948,36 @@
         </is>
       </c>
     </row>
+    <row outlineLevel="0" r="53">
+      <c r="A53" s="0">
+        <v>53</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>Joglekar et al 2025</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="54">
+      <c r="A54" s="0">
+        <v>54</v>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>Nkosi et al 2026</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="55">
+      <c r="A55" s="0">
+        <v>55</v>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>Thanh et al 2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
